--- a/data/Polaris/Comentários Polaris.xlsx
+++ b/data/Polaris/Comentários Polaris.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gridcobr.sharepoint.com/sites/GRIDCO/Shared Documents/Gridco/17. Acesso Externo Thopen/3. Polaris/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1503" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B875D1-F57B-4830-B065-3C813C209DCB}"/>
+  <xr:revisionPtr revIDLastSave="1508" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF8F47B-CCE9-49A3-A1D3-DE2A9C33B570}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C1E55A4-6A58-4802-A746-28D27D2A414B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Comentários" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1439,9 +1439,6 @@
     <t>Usina - Usina Deslgada, Relé Trip 27Abc - 27/06/2026 14:40 às 27/06/2026 21:00</t>
   </si>
   <si>
-    <t>Piancó</t>
-  </si>
-  <si>
     <t>Usina desligada devido falta de pagamento da fatura da concessionaria - de 28/05 até 09/06</t>
   </si>
   <si>
@@ -1776,6 +1773,9 @@
   </si>
   <si>
     <t>16MIN</t>
+  </si>
+  <si>
+    <t>Piancó 1</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1786,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2009,13 +2009,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9E4F17D-0891-4D97-BD59-CCE6BD4838CF}" name="Tabela6" displayName="Tabela6" ref="B1:D539" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="B1:D539" xr:uid="{CF14C9BA-A6A7-4BFD-A3C9-7EE7822230DB}">
-    <filterColumn colId="1">
-      <filters>
-        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:D539" xr:uid="{CF14C9BA-A6A7-4BFD-A3C9-7EE7822230DB}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3840FEB7-BDFC-463D-A309-4251464A7403}" name="UFV 1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{222368D3-AF3F-4BEB-99BE-527F836A68C8}" name="Data" dataDxfId="1"/>
@@ -2026,9 +2020,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2066,7 +2060,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2172,7 +2166,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2314,7 +2308,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2326,17 +2320,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="B1:D539"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1"/>
-    <col min="2" max="2" width="34.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="113.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="95.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="34.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="113.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="95.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="14.25" customHeight="1">
+    <row r="1" spans="2:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2347,7 +2341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:4" hidden="1">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2358,7 +2352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4" hidden="1">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2369,7 +2363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:4" hidden="1">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="28.9" hidden="1">
+    <row r="5" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2391,7 +2385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:4" hidden="1">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -2402,7 +2396,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="28.9" hidden="1">
+    <row r="7" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2413,7 +2407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:4" hidden="1">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:4" hidden="1">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -2433,7 +2427,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="2:4" hidden="1">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:4" hidden="1">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2455,7 +2449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:4" hidden="1">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
@@ -2466,7 +2460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:4" hidden="1">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:4" hidden="1">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -2488,7 +2482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:4" hidden="1">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
@@ -2499,7 +2493,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:4" hidden="1">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
@@ -2510,7 +2504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:4" hidden="1">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2521,7 +2515,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:4" hidden="1">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -2532,7 +2526,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:4" hidden="1">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2543,7 +2537,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:4" hidden="1">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
@@ -2554,7 +2548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="28.9" hidden="1">
+    <row r="21" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -2565,7 +2559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:4" hidden="1">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
@@ -2576,7 +2570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:4" hidden="1">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
@@ -2587,7 +2581,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="2:4" hidden="1">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
@@ -2598,7 +2592,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:4" hidden="1">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
@@ -2609,7 +2603,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:4" hidden="1">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
@@ -2620,7 +2614,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:4" hidden="1">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
@@ -2631,7 +2625,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:4" hidden="1">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>33</v>
       </c>
@@ -2642,7 +2636,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:4" hidden="1">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>37</v>
       </c>
@@ -2653,7 +2647,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:4" hidden="1">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
@@ -2664,7 +2658,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
@@ -2675,7 +2669,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="2:4" hidden="1">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
@@ -2686,7 +2680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="2:4" hidden="1">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
@@ -2697,7 +2691,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="2:4" hidden="1">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
@@ -2708,7 +2702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="2:4" hidden="1">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
@@ -2719,7 +2713,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:4" hidden="1">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
@@ -2730,7 +2724,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="2:4" hidden="1">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
@@ -2741,7 +2735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="2:4" hidden="1">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>31</v>
       </c>
@@ -2752,7 +2746,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="2:4" hidden="1">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2757,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:4" hidden="1">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
@@ -2774,7 +2768,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="2:4" hidden="1">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,7 +2779,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="2:4" hidden="1">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
@@ -2796,7 +2790,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="2:4" hidden="1">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
@@ -2807,7 +2801,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:4" hidden="1">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>31</v>
       </c>
@@ -2818,7 +2812,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:4" hidden="1">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>42</v>
       </c>
@@ -2829,7 +2823,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="2:4" hidden="1">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
@@ -2840,7 +2834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="2:4" hidden="1">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>60</v>
       </c>
@@ -2851,7 +2845,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="2:4" hidden="1">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>18</v>
       </c>
@@ -2862,7 +2856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="2:4" hidden="1">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>13</v>
       </c>
@@ -2873,7 +2867,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="2:4" hidden="1">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
@@ -2884,7 +2878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="2:4" hidden="1">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
@@ -2895,7 +2889,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="2:4" hidden="1">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
@@ -2906,7 +2900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:4" hidden="1">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>9</v>
       </c>
@@ -2917,7 +2911,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="2:4" hidden="1">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -2928,7 +2922,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="2:4" hidden="1">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>3</v>
       </c>
@@ -2939,7 +2933,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="2:4" hidden="1">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,7 +2944,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="2:4" hidden="1">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
@@ -2961,7 +2955,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:4" hidden="1">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>31</v>
       </c>
@@ -2972,7 +2966,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="2:4" hidden="1">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>31</v>
       </c>
@@ -2983,7 +2977,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="2:4" hidden="1">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>42</v>
       </c>
@@ -2994,7 +2988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="2:4" hidden="1">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,7 +2999,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:4" hidden="1">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:4" hidden="1">
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
@@ -3027,7 +3021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="2:4" hidden="1">
+    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
         <v>18</v>
       </c>
@@ -3038,7 +3032,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="2:4" hidden="1">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>42</v>
       </c>
@@ -3049,7 +3043,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="2:4" hidden="1">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
@@ -3060,7 +3054,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="2:4" hidden="1">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>3</v>
       </c>
@@ -3071,7 +3065,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="2:4" hidden="1">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>22</v>
       </c>
@@ -3082,7 +3076,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:4" hidden="1">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>49</v>
       </c>
@@ -3093,7 +3087,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:4" hidden="1">
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>33</v>
       </c>
@@ -3104,7 +3098,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="2:4" hidden="1">
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
         <v>37</v>
       </c>
@@ -3115,7 +3109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="2:4" hidden="1">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -3126,7 +3120,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="2:4" hidden="1">
+    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
         <v>3</v>
       </c>
@@ -3137,7 +3131,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="2:4" hidden="1">
+    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>22</v>
       </c>
@@ -3148,7 +3142,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="2:4" hidden="1">
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>60</v>
       </c>
@@ -3159,7 +3153,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="2:4" hidden="1">
+    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>18</v>
       </c>
@@ -3170,7 +3164,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="2:4" hidden="1">
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>18</v>
       </c>
@@ -3181,7 +3175,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="2:4" hidden="1">
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>13</v>
       </c>
@@ -3192,7 +3186,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="2:4" hidden="1">
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>31</v>
       </c>
@@ -3203,7 +3197,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="2:4" hidden="1">
+    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
@@ -3214,7 +3208,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="81" spans="2:4" hidden="1">
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
         <v>18</v>
       </c>
@@ -3225,7 +3219,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="2:4" hidden="1">
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
@@ -3236,7 +3230,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="2:4" hidden="1">
+    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>92</v>
       </c>
@@ -3247,7 +3241,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="2:4" hidden="1">
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>31</v>
       </c>
@@ -3258,7 +3252,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="2:4" hidden="1">
+    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>33</v>
       </c>
@@ -3269,7 +3263,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="2:4" hidden="1">
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
@@ -3280,7 +3274,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="2:4" hidden="1">
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
@@ -3291,7 +3285,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="2:4" hidden="1">
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>25</v>
       </c>
@@ -3302,7 +3296,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="2:4" hidden="1">
+    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
@@ -3313,7 +3307,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="2:4" hidden="1">
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
@@ -3324,7 +3318,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="91" spans="2:4" hidden="1">
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
         <v>5</v>
       </c>
@@ -3335,7 +3329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="2:4" hidden="1">
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
         <v>92</v>
       </c>
@@ -3346,7 +3340,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="2:4" hidden="1">
+    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
         <v>33</v>
       </c>
@@ -3357,7 +3351,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="94" spans="2:4" hidden="1">
+    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
@@ -3368,7 +3362,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="95" spans="2:4" hidden="1">
+    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>60</v>
       </c>
@@ -3379,7 +3373,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="2:4" hidden="1">
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
         <v>3</v>
       </c>
@@ -3390,7 +3384,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="97" spans="2:4" hidden="1">
+    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
@@ -3401,7 +3395,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="2:4" hidden="1">
+    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
         <v>3</v>
       </c>
@@ -3412,7 +3406,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="99" spans="2:4" hidden="1">
+    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
         <v>22</v>
       </c>
@@ -3423,7 +3417,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="100" spans="2:4" hidden="1">
+    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
         <v>3</v>
       </c>
@@ -3434,7 +3428,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="2:4" hidden="1">
+    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
         <v>22</v>
       </c>
@@ -3445,7 +3439,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="2:4" hidden="1">
+    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
         <v>22</v>
       </c>
@@ -3456,7 +3450,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="2:4" hidden="1">
+    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>107</v>
       </c>
@@ -3467,7 +3461,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="104" spans="2:4" hidden="1">
+    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>3</v>
       </c>
@@ -3478,7 +3472,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="2:4" hidden="1">
+    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
         <v>22</v>
       </c>
@@ -3489,7 +3483,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="106" spans="2:4" ht="13.15" hidden="1" customHeight="1">
+    <row r="106" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
         <v>18</v>
       </c>
@@ -3500,7 +3494,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="2:4" hidden="1">
+    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
         <v>5</v>
       </c>
@@ -3511,7 +3505,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="108" spans="2:4" hidden="1">
+    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
         <v>92</v>
       </c>
@@ -3522,7 +3516,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="2:4" hidden="1">
+    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
         <v>25</v>
       </c>
@@ -3533,7 +3527,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="2:4" hidden="1">
+    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
         <v>29</v>
       </c>
@@ -3544,7 +3538,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="2:4" hidden="1">
+    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
         <v>22</v>
       </c>
@@ -3555,7 +3549,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="2:4" hidden="1">
+    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
         <v>18</v>
       </c>
@@ -3566,7 +3560,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="2:4" hidden="1">
+    <row r="113" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
@@ -3577,7 +3571,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="2:4" hidden="1">
+    <row r="114" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
         <v>31</v>
       </c>
@@ -3588,7 +3582,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="2:4" hidden="1">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
@@ -3599,7 +3593,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="2:4" hidden="1">
+    <row r="116" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,7 +3604,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="2:4" hidden="1">
+    <row r="117" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
         <v>60</v>
       </c>
@@ -3621,7 +3615,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="2:4" hidden="1">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
         <v>25</v>
       </c>
@@ -3632,7 +3626,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="2:4" hidden="1">
+    <row r="119" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
         <v>107</v>
       </c>
@@ -3643,7 +3637,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="2:4" hidden="1">
+    <row r="120" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
         <v>31</v>
       </c>
@@ -3654,7 +3648,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="2:4" hidden="1">
+    <row r="121" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
         <v>125</v>
       </c>
@@ -3665,7 +3659,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="2:4" hidden="1">
+    <row r="122" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
         <v>125</v>
       </c>
@@ -3676,7 +3670,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="2:4" hidden="1">
+    <row r="123" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
         <v>128</v>
       </c>
@@ -3687,7 +3681,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="2:4" hidden="1">
+    <row r="124" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
         <v>25</v>
       </c>
@@ -3698,7 +3692,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="125" spans="2:4" hidden="1">
+    <row r="125" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
         <v>29</v>
       </c>
@@ -3709,7 +3703,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="126" spans="2:4" hidden="1">
+    <row r="126" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
         <v>128</v>
       </c>
@@ -3720,7 +3714,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="127" spans="2:4" hidden="1">
+    <row r="127" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
         <v>3</v>
       </c>
@@ -3731,7 +3725,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="128" spans="2:4" hidden="1">
+    <row r="128" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
         <v>22</v>
       </c>
@@ -3742,7 +3736,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="2:4" hidden="1">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
         <v>33</v>
       </c>
@@ -3753,7 +3747,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="2:4" hidden="1">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
@@ -3764,7 +3758,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="2:4" hidden="1">
+    <row r="131" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
         <v>33</v>
       </c>
@@ -3775,7 +3769,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="2:4" hidden="1">
+    <row r="132" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
         <v>37</v>
       </c>
@@ -3786,7 +3780,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="2:4" hidden="1">
+    <row r="133" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
         <v>11</v>
       </c>
@@ -3797,7 +3791,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="134" spans="2:4" hidden="1">
+    <row r="134" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
         <v>7</v>
       </c>
@@ -3808,7 +3802,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="135" spans="2:4" hidden="1">
+    <row r="135" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
         <v>138</v>
       </c>
@@ -3819,7 +3813,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="2:4" hidden="1">
+    <row r="136" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
         <v>33</v>
       </c>
@@ -3830,7 +3824,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="2:4" hidden="1">
+    <row r="137" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
         <v>33</v>
       </c>
@@ -3841,7 +3835,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="2:4" hidden="1">
+    <row r="138" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
@@ -3852,7 +3846,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="2:4" hidden="1">
+    <row r="139" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
         <v>37</v>
       </c>
@@ -3863,7 +3857,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="140" spans="2:4" hidden="1">
+    <row r="140" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
         <v>33</v>
       </c>
@@ -3874,7 +3868,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="2:4" hidden="1">
+    <row r="141" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
         <v>37</v>
       </c>
@@ -3885,7 +3879,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="2:4" hidden="1">
+    <row r="142" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
         <v>31</v>
       </c>
@@ -3896,7 +3890,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" spans="2:4" hidden="1">
+    <row r="143" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
         <v>18</v>
       </c>
@@ -3907,7 +3901,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="144" spans="2:4" hidden="1">
+    <row r="144" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
         <v>125</v>
       </c>
@@ -3918,7 +3912,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" spans="2:4" hidden="1">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
         <v>3</v>
       </c>
@@ -3929,7 +3923,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="146" spans="2:4" hidden="1">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
         <v>22</v>
       </c>
@@ -3940,7 +3934,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="2:4" hidden="1">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
         <v>18</v>
       </c>
@@ -3951,7 +3945,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="2:4" hidden="1">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
         <v>33</v>
       </c>
@@ -3962,7 +3956,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="2:4" hidden="1">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
         <v>37</v>
       </c>
@@ -3973,7 +3967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="2:4" hidden="1">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
         <v>125</v>
       </c>
@@ -3984,7 +3978,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="2:4" hidden="1">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
         <v>22</v>
       </c>
@@ -3995,7 +3989,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="2:4" hidden="1">
+    <row r="152" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
         <v>7</v>
       </c>
@@ -4006,7 +4000,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="2:4" hidden="1">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
         <v>33</v>
       </c>
@@ -4017,7 +4011,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="2:4" hidden="1">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
         <v>37</v>
       </c>
@@ -4028,7 +4022,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="2:4" hidden="1">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
         <v>3</v>
       </c>
@@ -4039,7 +4033,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="2:4" hidden="1">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
         <v>22</v>
       </c>
@@ -4050,7 +4044,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="2:4" hidden="1">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
@@ -4061,7 +4055,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="2:4" hidden="1">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
         <v>125</v>
       </c>
@@ -4072,7 +4066,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="2:4" hidden="1">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
         <v>3</v>
       </c>
@@ -4083,7 +4077,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="2:4" hidden="1">
+    <row r="160" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
         <v>22</v>
       </c>
@@ -4094,7 +4088,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="161" spans="2:4" hidden="1">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
         <v>157</v>
       </c>
@@ -4105,7 +4099,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="2:4" hidden="1">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
         <v>13</v>
       </c>
@@ -4116,7 +4110,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="163" spans="2:4" hidden="1">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
         <v>92</v>
       </c>
@@ -4127,7 +4121,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="164" spans="2:4" hidden="1">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
         <v>33</v>
       </c>
@@ -4138,7 +4132,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="2:4" hidden="1">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
         <v>37</v>
       </c>
@@ -4149,7 +4143,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="166" spans="2:4" hidden="1">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
         <v>3</v>
       </c>
@@ -4160,7 +4154,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="167" spans="2:4" hidden="1">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
         <v>22</v>
       </c>
@@ -4171,7 +4165,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="168" spans="2:4" hidden="1">
+    <row r="168" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
         <v>22</v>
       </c>
@@ -4182,7 +4176,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="169" spans="2:4" hidden="1">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B169" s="1" t="s">
         <v>107</v>
       </c>
@@ -4193,7 +4187,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="170" spans="2:4" hidden="1">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B170" s="1" t="s">
         <v>22</v>
       </c>
@@ -4204,7 +4198,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="171" spans="2:4" hidden="1">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B171" s="1" t="s">
         <v>7</v>
       </c>
@@ -4215,7 +4209,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="172" spans="2:4" hidden="1">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B172" s="1" t="s">
         <v>33</v>
       </c>
@@ -4226,7 +4220,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="173" spans="2:4" hidden="1">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B173" s="1" t="s">
         <v>3</v>
       </c>
@@ -4237,7 +4231,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="174" spans="2:4" hidden="1">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B174" s="1" t="s">
         <v>5</v>
       </c>
@@ -4248,7 +4242,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="175" spans="2:4" hidden="1">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B175" s="1" t="s">
         <v>33</v>
       </c>
@@ -4259,7 +4253,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="176" spans="2:4" hidden="1">
+    <row r="176" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B176" s="1" t="s">
         <v>107</v>
       </c>
@@ -4270,7 +4264,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="177" spans="2:4" hidden="1">
+    <row r="177" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B177" s="1" t="s">
         <v>11</v>
       </c>
@@ -4281,7 +4275,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="178" spans="2:4" hidden="1">
+    <row r="178" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B178" s="1" t="s">
         <v>33</v>
       </c>
@@ -4292,7 +4286,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="179" spans="2:4" hidden="1">
+    <row r="179" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B179" s="1" t="s">
         <v>5</v>
       </c>
@@ -4303,7 +4297,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="180" spans="2:4" hidden="1">
+    <row r="180" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B180" s="1" t="s">
         <v>92</v>
       </c>
@@ -4314,7 +4308,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="181" spans="2:4" hidden="1">
+    <row r="181" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B181" s="1" t="s">
         <v>33</v>
       </c>
@@ -4325,7 +4319,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="182" spans="2:4" hidden="1">
+    <row r="182" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B182" s="1" t="s">
         <v>33</v>
       </c>
@@ -4336,7 +4330,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="183" spans="2:4" hidden="1">
+    <row r="183" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B183" s="1" t="s">
         <v>5</v>
       </c>
@@ -4347,7 +4341,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="184" spans="2:4" hidden="1">
+    <row r="184" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B184" s="1" t="s">
         <v>92</v>
       </c>
@@ -4358,7 +4352,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="185" spans="2:4" hidden="1">
+    <row r="185" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B185" s="1" t="s">
         <v>31</v>
       </c>
@@ -4369,7 +4363,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="186" spans="2:4" hidden="1">
+    <row r="186" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B186" s="1" t="s">
         <v>33</v>
       </c>
@@ -4380,7 +4374,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="187" spans="2:4" ht="13.9" hidden="1" customHeight="1">
+    <row r="187" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="1" t="s">
         <v>37</v>
       </c>
@@ -4391,7 +4385,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="188" spans="2:4" ht="13.9" hidden="1" customHeight="1">
+    <row r="188" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
@@ -4402,7 +4396,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="189" spans="2:4" ht="13.9" hidden="1" customHeight="1">
+    <row r="189" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="1" t="s">
         <v>33</v>
       </c>
@@ -4413,7 +4407,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="190" spans="2:4" hidden="1">
+    <row r="190" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B190" s="1" t="s">
         <v>33</v>
       </c>
@@ -4424,7 +4418,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="191" spans="2:4" hidden="1">
+    <row r="191" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B191" s="1" t="s">
         <v>37</v>
       </c>
@@ -4435,7 +4429,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="192" spans="2:4" hidden="1">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B192" s="1" t="s">
         <v>37</v>
       </c>
@@ -4446,7 +4440,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="193" spans="2:4" hidden="1">
+    <row r="193" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B193" s="1" t="s">
         <v>25</v>
       </c>
@@ -4457,7 +4451,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="194" spans="2:4" hidden="1">
+    <row r="194" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B194" s="1" t="s">
         <v>33</v>
       </c>
@@ -4468,7 +4462,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="195" spans="2:4" hidden="1">
+    <row r="195" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B195" s="1" t="s">
         <v>33</v>
       </c>
@@ -4479,7 +4473,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="196" spans="2:4" hidden="1">
+    <row r="196" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B196" s="1" t="s">
         <v>37</v>
       </c>
@@ -4490,7 +4484,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="197" spans="2:4" hidden="1">
+    <row r="197" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B197" s="1" t="s">
         <v>37</v>
       </c>
@@ -4501,7 +4495,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="198" spans="2:4" hidden="1">
+    <row r="198" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B198" s="1" t="s">
         <v>60</v>
       </c>
@@ -4512,7 +4506,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="199" spans="2:4" hidden="1">
+    <row r="199" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B199" s="1" t="s">
         <v>3</v>
       </c>
@@ -4523,7 +4517,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="200" spans="2:4" hidden="1">
+    <row r="200" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B200" s="1" t="s">
         <v>22</v>
       </c>
@@ -4534,7 +4528,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="201" spans="2:4" hidden="1">
+    <row r="201" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B201" s="1" t="s">
         <v>31</v>
       </c>
@@ -4545,7 +4539,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="202" spans="2:4" hidden="1">
+    <row r="202" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B202" s="1" t="s">
         <v>3</v>
       </c>
@@ -4556,7 +4550,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="203" spans="2:4" hidden="1">
+    <row r="203" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B203" s="1" t="s">
         <v>22</v>
       </c>
@@ -4567,7 +4561,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="204" spans="2:4" hidden="1">
+    <row r="204" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B204" s="1" t="s">
         <v>33</v>
       </c>
@@ -4578,7 +4572,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="205" spans="2:4" hidden="1">
+    <row r="205" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B205" s="1" t="s">
         <v>37</v>
       </c>
@@ -4589,7 +4583,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="2:4" hidden="1">
+    <row r="206" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B206" s="1" t="s">
         <v>5</v>
       </c>
@@ -4600,7 +4594,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="207" spans="2:4" hidden="1">
+    <row r="207" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B207" s="1" t="s">
         <v>33</v>
       </c>
@@ -4611,7 +4605,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="208" spans="2:4" hidden="1">
+    <row r="208" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B208" s="1" t="s">
         <v>49</v>
       </c>
@@ -4622,7 +4616,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="209" spans="2:4" hidden="1">
+    <row r="209" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B209" s="1" t="s">
         <v>22</v>
       </c>
@@ -4633,7 +4627,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="210" spans="2:4" hidden="1">
+    <row r="210" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B210" s="1" t="s">
         <v>3</v>
       </c>
@@ -4644,7 +4638,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="211" spans="2:4" hidden="1">
+    <row r="211" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B211" s="1" t="s">
         <v>22</v>
       </c>
@@ -4655,7 +4649,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="212" spans="2:4" hidden="1">
+    <row r="212" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B212" s="1" t="s">
         <v>128</v>
       </c>
@@ -4666,7 +4660,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="213" spans="2:4" hidden="1">
+    <row r="213" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B213" s="1" t="s">
         <v>9</v>
       </c>
@@ -4677,7 +4671,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="214" spans="2:4" hidden="1">
+    <row r="214" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B214" s="1" t="s">
         <v>18</v>
       </c>
@@ -4688,7 +4682,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="215" spans="2:4" hidden="1">
+    <row r="215" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B215" s="1" t="s">
         <v>18</v>
       </c>
@@ -4699,7 +4693,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="216" spans="2:4" hidden="1">
+    <row r="216" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B216" s="1" t="s">
         <v>22</v>
       </c>
@@ -4710,7 +4704,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="217" spans="2:4" hidden="1">
+    <row r="217" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B217" s="1" t="s">
         <v>3</v>
       </c>
@@ -4721,7 +4715,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="218" spans="2:4" hidden="1">
+    <row r="218" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B218" s="1" t="s">
         <v>22</v>
       </c>
@@ -4732,7 +4726,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="219" spans="2:4" hidden="1">
+    <row r="219" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B219" s="1" t="s">
         <v>3</v>
       </c>
@@ -4743,7 +4737,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="220" spans="2:4" hidden="1">
+    <row r="220" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B220" s="1" t="s">
         <v>18</v>
       </c>
@@ -4754,7 +4748,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="221" spans="2:4" hidden="1">
+    <row r="221" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B221" s="1" t="s">
         <v>7</v>
       </c>
@@ -4765,7 +4759,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="222" spans="2:4" hidden="1">
+    <row r="222" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B222" s="1" t="s">
         <v>33</v>
       </c>
@@ -4776,7 +4770,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="223" spans="2:4" hidden="1">
+    <row r="223" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B223" s="1" t="s">
         <v>37</v>
       </c>
@@ -4787,7 +4781,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="224" spans="2:4" hidden="1">
+    <row r="224" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B224" s="1" t="s">
         <v>92</v>
       </c>
@@ -4798,7 +4792,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="225" spans="2:4" hidden="1">
+    <row r="225" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B225" s="1" t="s">
         <v>3</v>
       </c>
@@ -4809,7 +4803,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="226" spans="2:4" hidden="1">
+    <row r="226" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B226" s="1" t="s">
         <v>7</v>
       </c>
@@ -4820,7 +4814,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="227" spans="2:4" hidden="1">
+    <row r="227" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B227" s="1" t="s">
         <v>3</v>
       </c>
@@ -4831,7 +4825,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="228" spans="2:4" hidden="1">
+    <row r="228" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B228" s="1" t="s">
         <v>5</v>
       </c>
@@ -4842,7 +4836,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="229" spans="2:4" hidden="1">
+    <row r="229" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B229" s="1" t="s">
         <v>92</v>
       </c>
@@ -4853,7 +4847,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="230" spans="2:4" hidden="1">
+    <row r="230" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B230" s="1" t="s">
         <v>22</v>
       </c>
@@ -4864,7 +4858,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="231" spans="2:4" hidden="1">
+    <row r="231" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B231" s="1" t="s">
         <v>3</v>
       </c>
@@ -4875,7 +4869,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="232" spans="2:4" hidden="1">
+    <row r="232" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B232" s="1" t="s">
         <v>138</v>
       </c>
@@ -4886,7 +4880,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="233" spans="2:4" hidden="1">
+    <row r="233" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B233" s="1" t="s">
         <v>31</v>
       </c>
@@ -4897,7 +4891,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="234" spans="2:4" hidden="1">
+    <row r="234" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B234" s="1" t="s">
         <v>33</v>
       </c>
@@ -4908,7 +4902,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="235" spans="2:4" hidden="1">
+    <row r="235" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B235" s="1" t="s">
         <v>37</v>
       </c>
@@ -4919,7 +4913,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="236" spans="2:4" hidden="1">
+    <row r="236" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B236" s="1" t="s">
         <v>33</v>
       </c>
@@ -4930,7 +4924,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="237" spans="2:4" hidden="1">
+    <row r="237" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B237" s="1" t="s">
         <v>49</v>
       </c>
@@ -4941,7 +4935,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="238" spans="2:4" hidden="1">
+    <row r="238" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B238" s="1" t="s">
         <v>33</v>
       </c>
@@ -4952,7 +4946,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="239" spans="2:4" hidden="1">
+    <row r="239" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B239" s="1" t="s">
         <v>11</v>
       </c>
@@ -4963,7 +4957,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="240" spans="2:4" hidden="1">
+    <row r="240" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B240" s="1" t="s">
         <v>33</v>
       </c>
@@ -4974,7 +4968,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="241" spans="2:4" hidden="1">
+    <row r="241" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B241" s="1" t="s">
         <v>37</v>
       </c>
@@ -4985,7 +4979,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="242" spans="2:4" hidden="1">
+    <row r="242" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B242" s="1" t="s">
         <v>107</v>
       </c>
@@ -4996,7 +4990,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="243" spans="2:4" hidden="1">
+    <row r="243" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B243" s="1" t="s">
         <v>125</v>
       </c>
@@ -5007,7 +5001,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="244" spans="2:4" hidden="1">
+    <row r="244" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B244" s="1" t="s">
         <v>11</v>
       </c>
@@ -5018,7 +5012,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="245" spans="2:4" hidden="1">
+    <row r="245" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B245" s="1" t="s">
         <v>37</v>
       </c>
@@ -5029,7 +5023,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="246" spans="2:4" hidden="1">
+    <row r="246" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B246" s="1" t="s">
         <v>11</v>
       </c>
@@ -5040,7 +5034,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="247" spans="2:4" hidden="1">
+    <row r="247" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B247" s="1" t="s">
         <v>44</v>
       </c>
@@ -5051,7 +5045,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="248" spans="2:4" ht="13.15" hidden="1" customHeight="1">
+    <row r="248" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="1" t="s">
         <v>33</v>
       </c>
@@ -5062,7 +5056,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="249" spans="2:4" ht="13.15" hidden="1" customHeight="1">
+    <row r="249" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="1" t="s">
         <v>138</v>
       </c>
@@ -5073,7 +5067,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="250" spans="2:4" hidden="1">
+    <row r="250" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B250" s="1" t="s">
         <v>42</v>
       </c>
@@ -5084,7 +5078,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="251" spans="2:4" hidden="1">
+    <row r="251" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B251" s="1" t="s">
         <v>33</v>
       </c>
@@ -5095,7 +5089,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="252" spans="2:4" hidden="1">
+    <row r="252" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B252" s="1" t="s">
         <v>33</v>
       </c>
@@ -5106,7 +5100,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="253" spans="2:4" hidden="1">
+    <row r="253" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B253" s="1" t="s">
         <v>37</v>
       </c>
@@ -5117,7 +5111,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="254" spans="2:4" hidden="1">
+    <row r="254" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B254" s="1" t="s">
         <v>125</v>
       </c>
@@ -5128,7 +5122,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="255" spans="2:4" hidden="1">
+    <row r="255" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B255" s="1" t="s">
         <v>33</v>
       </c>
@@ -5139,7 +5133,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="256" spans="2:4" hidden="1">
+    <row r="256" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B256" s="1" t="s">
         <v>37</v>
       </c>
@@ -5150,7 +5144,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="257" spans="2:4" hidden="1">
+    <row r="257" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B257" s="1" t="s">
         <v>9</v>
       </c>
@@ -5161,7 +5155,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="258" spans="2:4" hidden="1">
+    <row r="258" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B258" s="1" t="s">
         <v>92</v>
       </c>
@@ -5172,7 +5166,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="259" spans="2:4" hidden="1">
+    <row r="259" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B259" s="1" t="s">
         <v>49</v>
       </c>
@@ -5183,7 +5177,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="260" spans="2:4" hidden="1">
+    <row r="260" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B260" s="1" t="s">
         <v>49</v>
       </c>
@@ -5194,7 +5188,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="261" spans="2:4" hidden="1">
+    <row r="261" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B261" s="1" t="s">
         <v>22</v>
       </c>
@@ -5205,7 +5199,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="262" spans="2:4" hidden="1">
+    <row r="262" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B262" s="1" t="s">
         <v>3</v>
       </c>
@@ -5216,7 +5210,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="263" spans="2:4" hidden="1">
+    <row r="263" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B263" s="1" t="s">
         <v>3</v>
       </c>
@@ -5227,7 +5221,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="264" spans="2:4" hidden="1">
+    <row r="264" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B264" s="1" t="s">
         <v>42</v>
       </c>
@@ -5238,7 +5232,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="265" spans="2:4" hidden="1">
+    <row r="265" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B265" s="1" t="s">
         <v>44</v>
       </c>
@@ -5249,7 +5243,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="266" spans="2:4" hidden="1">
+    <row r="266" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B266" s="1" t="s">
         <v>31</v>
       </c>
@@ -5260,7 +5254,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="267" spans="2:4" hidden="1">
+    <row r="267" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B267" s="1" t="s">
         <v>33</v>
       </c>
@@ -5271,7 +5265,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="268" spans="2:4" hidden="1">
+    <row r="268" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B268" s="1" t="s">
         <v>37</v>
       </c>
@@ -5282,7 +5276,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="269" spans="2:4" hidden="1">
+    <row r="269" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B269" s="1" t="s">
         <v>44</v>
       </c>
@@ -5293,7 +5287,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="270" spans="2:4" hidden="1">
+    <row r="270" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B270" s="1" t="s">
         <v>22</v>
       </c>
@@ -5304,7 +5298,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="271" spans="2:4" hidden="1">
+    <row r="271" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B271" s="1" t="s">
         <v>3</v>
       </c>
@@ -5315,7 +5309,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="272" spans="2:4" hidden="1">
+    <row r="272" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B272" s="1" t="s">
         <v>49</v>
       </c>
@@ -5326,7 +5320,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="273" spans="2:4" hidden="1">
+    <row r="273" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B273" s="1" t="s">
         <v>33</v>
       </c>
@@ -5337,7 +5331,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="274" spans="2:4" hidden="1">
+    <row r="274" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B274" s="1" t="s">
         <v>37</v>
       </c>
@@ -5348,7 +5342,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="275" spans="2:4" hidden="1">
+    <row r="275" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B275" s="1" t="s">
         <v>31</v>
       </c>
@@ -5359,7 +5353,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="276" spans="2:4" hidden="1">
+    <row r="276" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B276" s="1" t="s">
         <v>5</v>
       </c>
@@ -5370,7 +5364,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="277" spans="2:4" hidden="1">
+    <row r="277" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B277" s="1" t="s">
         <v>92</v>
       </c>
@@ -5381,7 +5375,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="278" spans="2:4" hidden="1">
+    <row r="278" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B278" s="1" t="s">
         <v>31</v>
       </c>
@@ -5392,7 +5386,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="279" spans="2:4" hidden="1">
+    <row r="279" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B279" s="1" t="s">
         <v>33</v>
       </c>
@@ -5403,7 +5397,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="280" spans="2:4" hidden="1">
+    <row r="280" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B280" s="1" t="s">
         <v>3</v>
       </c>
@@ -5414,7 +5408,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="281" spans="2:4" hidden="1">
+    <row r="281" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B281" s="1" t="s">
         <v>22</v>
       </c>
@@ -5425,7 +5419,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="282" spans="2:4" hidden="1">
+    <row r="282" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B282" s="1" t="s">
         <v>5</v>
       </c>
@@ -5436,7 +5430,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="283" spans="2:4" hidden="1">
+    <row r="283" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B283" s="1" t="s">
         <v>92</v>
       </c>
@@ -5447,7 +5441,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="284" spans="2:4" hidden="1">
+    <row r="284" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B284" s="1" t="s">
         <v>107</v>
       </c>
@@ -5458,7 +5452,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="285" spans="2:4" hidden="1">
+    <row r="285" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B285" s="1" t="s">
         <v>3</v>
       </c>
@@ -5469,7 +5463,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="286" spans="2:4" hidden="1">
+    <row r="286" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B286" s="1" t="s">
         <v>22</v>
       </c>
@@ -5480,7 +5474,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="287" spans="2:4" hidden="1">
+    <row r="287" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B287" s="1" t="s">
         <v>128</v>
       </c>
@@ -5491,7 +5485,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="288" spans="2:4" hidden="1">
+    <row r="288" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B288" s="1" t="s">
         <v>138</v>
       </c>
@@ -5502,7 +5496,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="289" spans="2:4" hidden="1">
+    <row r="289" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B289" s="1" t="s">
         <v>11</v>
       </c>
@@ -5513,7 +5507,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="290" spans="2:4" hidden="1">
+    <row r="290" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B290" s="1" t="s">
         <v>125</v>
       </c>
@@ -5524,7 +5518,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="291" spans="2:4" hidden="1">
+    <row r="291" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B291" s="1" t="s">
         <v>157</v>
       </c>
@@ -5535,7 +5529,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="292" spans="2:4" hidden="1">
+    <row r="292" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B292" s="1" t="s">
         <v>18</v>
       </c>
@@ -5546,7 +5540,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="293" spans="2:4" hidden="1">
+    <row r="293" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B293" s="1" t="s">
         <v>128</v>
       </c>
@@ -5557,7 +5551,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="294" spans="2:4" hidden="1">
+    <row r="294" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B294" s="1" t="s">
         <v>31</v>
       </c>
@@ -5568,7 +5562,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="295" spans="2:4" hidden="1">
+    <row r="295" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B295" s="1" t="s">
         <v>33</v>
       </c>
@@ -5579,7 +5573,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="296" spans="2:4" hidden="1">
+    <row r="296" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B296" s="1" t="s">
         <v>37</v>
       </c>
@@ -5590,7 +5584,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="297" spans="2:4" hidden="1">
+    <row r="297" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B297" s="1" t="s">
         <v>138</v>
       </c>
@@ -5601,7 +5595,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="298" spans="2:4" hidden="1">
+    <row r="298" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B298" s="1" t="s">
         <v>3</v>
       </c>
@@ -5612,7 +5606,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="299" spans="2:4" hidden="1">
+    <row r="299" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B299" s="1" t="s">
         <v>22</v>
       </c>
@@ -5623,7 +5617,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="300" spans="2:4" hidden="1">
+    <row r="300" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B300" s="1" t="s">
         <v>157</v>
       </c>
@@ -5634,7 +5628,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="301" spans="2:4" ht="28.9" hidden="1">
+    <row r="301" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B301" s="1" t="s">
         <v>33</v>
       </c>
@@ -5645,7 +5639,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="302" spans="2:4" ht="28.9" hidden="1">
+    <row r="302" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B302" s="1" t="s">
         <v>37</v>
       </c>
@@ -5656,7 +5650,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="303" spans="2:4" hidden="1">
+    <row r="303" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B303" s="1" t="s">
         <v>157</v>
       </c>
@@ -5667,7 +5661,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="304" spans="2:4" hidden="1">
+    <row r="304" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B304" s="1" t="s">
         <v>13</v>
       </c>
@@ -5678,7 +5672,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="305" spans="2:4" hidden="1">
+    <row r="305" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B305" s="1" t="s">
         <v>5</v>
       </c>
@@ -5689,7 +5683,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="306" spans="2:4" hidden="1">
+    <row r="306" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B306" s="1" t="s">
         <v>60</v>
       </c>
@@ -5700,7 +5694,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="307" spans="2:4" hidden="1">
+    <row r="307" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B307" s="1" t="s">
         <v>13</v>
       </c>
@@ -5711,7 +5705,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="308" spans="2:4" hidden="1">
+    <row r="308" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B308" s="1" t="s">
         <v>33</v>
       </c>
@@ -5722,7 +5716,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="309" spans="2:4" hidden="1">
+    <row r="309" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B309" s="1" t="s">
         <v>37</v>
       </c>
@@ -5733,7 +5727,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="310" spans="2:4" hidden="1">
+    <row r="310" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B310" s="1" t="s">
         <v>18</v>
       </c>
@@ -5744,7 +5738,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="311" spans="2:4" hidden="1">
+    <row r="311" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B311" s="1" t="s">
         <v>92</v>
       </c>
@@ -5755,7 +5749,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="312" spans="2:4" hidden="1">
+    <row r="312" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B312" s="1" t="s">
         <v>5</v>
       </c>
@@ -5766,7 +5760,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="313" spans="2:4" hidden="1">
+    <row r="313" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B313" s="1" t="s">
         <v>92</v>
       </c>
@@ -5777,7 +5771,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="314" spans="2:4" hidden="1">
+    <row r="314" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B314" s="1" t="s">
         <v>11</v>
       </c>
@@ -5788,7 +5782,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="315" spans="2:4" hidden="1">
+    <row r="315" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B315" s="1" t="s">
         <v>92</v>
       </c>
@@ -5799,7 +5793,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="316" spans="2:4" hidden="1">
+    <row r="316" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B316" s="1" t="s">
         <v>31</v>
       </c>
@@ -5810,7 +5804,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="317" spans="2:4" hidden="1">
+    <row r="317" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B317" s="1" t="s">
         <v>9</v>
       </c>
@@ -5821,7 +5815,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="318" spans="2:4" hidden="1">
+    <row r="318" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B318" s="1" t="s">
         <v>31</v>
       </c>
@@ -5832,7 +5826,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="319" spans="2:4" hidden="1">
+    <row r="319" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B319" s="1" t="s">
         <v>125</v>
       </c>
@@ -5843,7 +5837,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="320" spans="2:4" hidden="1">
+    <row r="320" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B320" s="1" t="s">
         <v>37</v>
       </c>
@@ -5854,7 +5848,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="321" spans="2:4" hidden="1">
+    <row r="321" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B321" s="1" t="s">
         <v>11</v>
       </c>
@@ -5865,7 +5859,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="322" spans="2:4" hidden="1">
+    <row r="322" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B322" s="1" t="s">
         <v>31</v>
       </c>
@@ -5876,7 +5870,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="323" spans="2:4" hidden="1">
+    <row r="323" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B323" s="1" t="s">
         <v>42</v>
       </c>
@@ -5887,7 +5881,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="324" spans="2:4" hidden="1">
+    <row r="324" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B324" s="1" t="s">
         <v>44</v>
       </c>
@@ -5898,7 +5892,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="325" spans="2:4" hidden="1">
+    <row r="325" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B325" s="1" t="s">
         <v>33</v>
       </c>
@@ -5909,7 +5903,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="326" spans="2:4" hidden="1">
+    <row r="326" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B326" s="1" t="s">
         <v>37</v>
       </c>
@@ -5920,7 +5914,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="327" spans="2:4" hidden="1">
+    <row r="327" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B327" s="1" t="s">
         <v>37</v>
       </c>
@@ -5931,7 +5925,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="328" spans="2:4" hidden="1">
+    <row r="328" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B328" s="1" t="s">
         <v>13</v>
       </c>
@@ -5942,7 +5936,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="329" spans="2:4" ht="28.9" hidden="1">
+    <row r="329" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B329" s="1" t="s">
         <v>138</v>
       </c>
@@ -5953,7 +5947,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="330" spans="2:4" hidden="1">
+    <row r="330" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B330" s="1" t="s">
         <v>60</v>
       </c>
@@ -5964,7 +5958,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="331" spans="2:4" hidden="1">
+    <row r="331" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B331" s="1" t="s">
         <v>3</v>
       </c>
@@ -5975,7 +5969,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="332" spans="2:4" hidden="1">
+    <row r="332" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B332" s="1" t="s">
         <v>33</v>
       </c>
@@ -5986,7 +5980,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="333" spans="2:4" hidden="1">
+    <row r="333" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B333" s="1" t="s">
         <v>37</v>
       </c>
@@ -5997,7 +5991,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="334" spans="2:4" hidden="1">
+    <row r="334" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B334" s="1" t="s">
         <v>3</v>
       </c>
@@ -6008,7 +6002,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="335" spans="2:4" hidden="1">
+    <row r="335" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B335" s="1" t="s">
         <v>22</v>
       </c>
@@ -6019,7 +6013,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="336" spans="2:4" hidden="1">
+    <row r="336" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B336" s="1" t="s">
         <v>13</v>
       </c>
@@ -6030,7 +6024,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="337" spans="2:4" hidden="1">
+    <row r="337" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B337" s="1" t="s">
         <v>107</v>
       </c>
@@ -6041,7 +6035,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="338" spans="2:4" hidden="1">
+    <row r="338" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B338" s="1" t="s">
         <v>11</v>
       </c>
@@ -6052,7 +6046,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="339" spans="2:4" hidden="1">
+    <row r="339" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B339" s="1" t="s">
         <v>7</v>
       </c>
@@ -6063,7 +6057,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="340" spans="2:4" hidden="1">
+    <row r="340" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B340" s="1" t="s">
         <v>33</v>
       </c>
@@ -6074,7 +6068,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="341" spans="2:4" hidden="1">
+    <row r="341" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B341" s="1" t="s">
         <v>37</v>
       </c>
@@ -6085,7 +6079,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="342" spans="2:4" hidden="1">
+    <row r="342" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B342" s="1" t="s">
         <v>3</v>
       </c>
@@ -6096,7 +6090,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="343" spans="2:4" hidden="1">
+    <row r="343" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B343" s="1" t="s">
         <v>22</v>
       </c>
@@ -6107,7 +6101,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="344" spans="2:4" hidden="1">
+    <row r="344" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B344" s="1" t="s">
         <v>7</v>
       </c>
@@ -6118,7 +6112,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="345" spans="2:4" hidden="1">
+    <row r="345" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B345" s="1" t="s">
         <v>9</v>
       </c>
@@ -6129,7 +6123,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="346" spans="2:4" hidden="1">
+    <row r="346" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B346" s="1" t="s">
         <v>18</v>
       </c>
@@ -6140,7 +6134,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="347" spans="2:4" hidden="1">
+    <row r="347" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B347" s="1" t="s">
         <v>7</v>
       </c>
@@ -6151,7 +6145,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="348" spans="2:4" hidden="1">
+    <row r="348" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B348" s="1" t="s">
         <v>5</v>
       </c>
@@ -6162,7 +6156,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="349" spans="2:4" hidden="1">
+    <row r="349" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B349" s="1" t="s">
         <v>5</v>
       </c>
@@ -6173,7 +6167,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="350" spans="2:4" hidden="1">
+    <row r="350" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B350" s="1" t="s">
         <v>5</v>
       </c>
@@ -6184,7 +6178,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="351" spans="2:4" hidden="1">
+    <row r="351" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B351" s="1" t="s">
         <v>92</v>
       </c>
@@ -6195,7 +6189,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="352" spans="2:4" hidden="1">
+    <row r="352" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B352" s="1" t="s">
         <v>92</v>
       </c>
@@ -6206,7 +6200,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="353" spans="2:4" hidden="1">
+    <row r="353" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B353" s="1" t="s">
         <v>92</v>
       </c>
@@ -6217,7 +6211,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="354" spans="2:4" hidden="1">
+    <row r="354" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B354" s="1" t="s">
         <v>92</v>
       </c>
@@ -6228,7 +6222,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="355" spans="2:4" hidden="1">
+    <row r="355" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B355" s="1" t="s">
         <v>25</v>
       </c>
@@ -6239,7 +6233,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="356" spans="2:4" hidden="1">
+    <row r="356" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B356" s="1" t="s">
         <v>25</v>
       </c>
@@ -6250,7 +6244,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="357" spans="2:4" hidden="1">
+    <row r="357" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B357" s="1" t="s">
         <v>25</v>
       </c>
@@ -6261,7 +6255,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="358" spans="2:4" hidden="1">
+    <row r="358" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B358" s="1" t="s">
         <v>29</v>
       </c>
@@ -6272,7 +6266,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="359" spans="2:4" hidden="1">
+    <row r="359" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B359" s="1" t="s">
         <v>29</v>
       </c>
@@ -6283,7 +6277,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="360" spans="2:4" hidden="1">
+    <row r="360" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B360" s="1" t="s">
         <v>107</v>
       </c>
@@ -6294,7 +6288,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="361" spans="2:4" hidden="1">
+    <row r="361" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B361" s="1" t="s">
         <v>107</v>
       </c>
@@ -6305,7 +6299,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="362" spans="2:4" hidden="1">
+    <row r="362" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B362" s="1" t="s">
         <v>31</v>
       </c>
@@ -6316,7 +6310,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="363" spans="2:4" hidden="1">
+    <row r="363" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B363" s="1" t="s">
         <v>31</v>
       </c>
@@ -6327,7 +6321,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="364" spans="2:4" hidden="1">
+    <row r="364" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B364" s="1" t="s">
         <v>31</v>
       </c>
@@ -6338,7 +6332,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="365" spans="2:4" hidden="1">
+    <row r="365" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B365" s="1" t="s">
         <v>31</v>
       </c>
@@ -6349,7 +6343,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="366" spans="2:4" hidden="1">
+    <row r="366" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B366" s="1" t="s">
         <v>31</v>
       </c>
@@ -6360,7 +6354,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="367" spans="2:4" hidden="1">
+    <row r="367" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B367" s="1" t="s">
         <v>31</v>
       </c>
@@ -6371,7 +6365,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="368" spans="2:4" hidden="1">
+    <row r="368" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B368" s="1" t="s">
         <v>31</v>
       </c>
@@ -6382,7 +6376,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="369" spans="2:4" hidden="1">
+    <row r="369" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B369" s="1" t="s">
         <v>31</v>
       </c>
@@ -6393,7 +6387,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="370" spans="2:4" hidden="1">
+    <row r="370" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B370" s="1" t="s">
         <v>31</v>
       </c>
@@ -6404,7 +6398,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="371" spans="2:4" hidden="1">
+    <row r="371" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B371" s="1" t="s">
         <v>31</v>
       </c>
@@ -6415,7 +6409,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="372" spans="2:4" hidden="1">
+    <row r="372" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B372" s="1" t="s">
         <v>31</v>
       </c>
@@ -6426,7 +6420,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="373" spans="2:4" hidden="1">
+    <row r="373" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B373" s="1" t="s">
         <v>31</v>
       </c>
@@ -6437,7 +6431,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="374" spans="2:4" hidden="1">
+    <row r="374" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B374" s="1" t="s">
         <v>337</v>
       </c>
@@ -6448,7 +6442,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="375" spans="2:4" hidden="1">
+    <row r="375" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B375" s="1" t="s">
         <v>337</v>
       </c>
@@ -6459,7 +6453,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="376" spans="2:4" hidden="1">
+    <row r="376" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B376" s="1" t="s">
         <v>337</v>
       </c>
@@ -6470,7 +6464,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="377" spans="2:4" hidden="1">
+    <row r="377" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B377" s="1" t="s">
         <v>341</v>
       </c>
@@ -6481,7 +6475,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="378" spans="2:4" hidden="1">
+    <row r="378" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B378" s="1" t="s">
         <v>42</v>
       </c>
@@ -6492,7 +6486,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="379" spans="2:4" hidden="1">
+    <row r="379" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B379" s="1" t="s">
         <v>42</v>
       </c>
@@ -6503,7 +6497,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="380" spans="2:4" hidden="1">
+    <row r="380" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B380" s="1" t="s">
         <v>42</v>
       </c>
@@ -6514,7 +6508,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="381" spans="2:4" hidden="1">
+    <row r="381" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B381" s="1" t="s">
         <v>42</v>
       </c>
@@ -6525,7 +6519,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="382" spans="2:4" hidden="1">
+    <row r="382" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B382" s="1" t="s">
         <v>42</v>
       </c>
@@ -6536,7 +6530,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="383" spans="2:4" hidden="1">
+    <row r="383" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B383" s="1" t="s">
         <v>44</v>
       </c>
@@ -6547,7 +6541,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="384" spans="2:4" hidden="1">
+    <row r="384" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B384" s="1" t="s">
         <v>44</v>
       </c>
@@ -6558,7 +6552,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="385" spans="2:4" hidden="1">
+    <row r="385" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B385" s="1" t="s">
         <v>37</v>
       </c>
@@ -6569,7 +6563,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="386" spans="2:4" hidden="1">
+    <row r="386" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B386" s="1" t="s">
         <v>33</v>
       </c>
@@ -6580,7 +6574,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="387" spans="2:4" hidden="1">
+    <row r="387" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B387" s="1" t="s">
         <v>33</v>
       </c>
@@ -6591,7 +6585,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="388" spans="2:4" hidden="1">
+    <row r="388" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B388" s="1" t="s">
         <v>33</v>
       </c>
@@ -6602,7 +6596,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="389" spans="2:4" hidden="1">
+    <row r="389" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B389" s="1" t="s">
         <v>33</v>
       </c>
@@ -6613,7 +6607,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="390" spans="2:4" hidden="1">
+    <row r="390" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B390" s="1" t="s">
         <v>33</v>
       </c>
@@ -6624,7 +6618,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="391" spans="2:4" hidden="1">
+    <row r="391" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B391" s="1" t="s">
         <v>33</v>
       </c>
@@ -6635,7 +6629,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="392" spans="2:4" hidden="1">
+    <row r="392" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B392" s="1" t="s">
         <v>33</v>
       </c>
@@ -6646,7 +6640,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="393" spans="2:4" hidden="1">
+    <row r="393" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B393" s="1" t="s">
         <v>33</v>
       </c>
@@ -6657,7 +6651,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="394" spans="2:4" hidden="1">
+    <row r="394" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B394" s="1" t="s">
         <v>33</v>
       </c>
@@ -6668,7 +6662,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="395" spans="2:4" hidden="1">
+    <row r="395" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B395" s="1" t="s">
         <v>33</v>
       </c>
@@ -6679,7 +6673,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="396" spans="2:4" hidden="1">
+    <row r="396" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B396" s="1" t="s">
         <v>37</v>
       </c>
@@ -6690,7 +6684,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="397" spans="2:4" hidden="1">
+    <row r="397" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B397" s="1" t="s">
         <v>37</v>
       </c>
@@ -6701,7 +6695,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="398" spans="2:4" hidden="1">
+    <row r="398" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B398" s="1" t="s">
         <v>37</v>
       </c>
@@ -6712,7 +6706,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="399" spans="2:4" hidden="1">
+    <row r="399" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B399" s="1" t="s">
         <v>37</v>
       </c>
@@ -6723,7 +6717,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="400" spans="2:4" hidden="1">
+    <row r="400" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B400" s="1" t="s">
         <v>37</v>
       </c>
@@ -6734,7 +6728,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="401" spans="2:4" hidden="1">
+    <row r="401" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B401" s="1" t="s">
         <v>37</v>
       </c>
@@ -6745,7 +6739,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="402" spans="2:4" hidden="1">
+    <row r="402" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B402" s="1" t="s">
         <v>37</v>
       </c>
@@ -6756,7 +6750,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="403" spans="2:4" hidden="1">
+    <row r="403" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B403" s="1" t="s">
         <v>37</v>
       </c>
@@ -6767,7 +6761,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="404" spans="2:4" hidden="1">
+    <row r="404" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B404" s="1" t="s">
         <v>37</v>
       </c>
@@ -6778,7 +6772,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="405" spans="2:4" hidden="1">
+    <row r="405" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B405" s="1" t="s">
         <v>125</v>
       </c>
@@ -6789,7 +6783,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="406" spans="2:4" hidden="1">
+    <row r="406" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B406" s="1" t="s">
         <v>11</v>
       </c>
@@ -6800,7 +6794,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="407" spans="2:4" hidden="1">
+    <row r="407" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B407" s="1" t="s">
         <v>11</v>
       </c>
@@ -6811,7 +6805,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="408" spans="2:4" hidden="1">
+    <row r="408" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B408" s="1" t="s">
         <v>11</v>
       </c>
@@ -6822,7 +6816,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="409" spans="2:4" hidden="1">
+    <row r="409" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B409" s="1" t="s">
         <v>11</v>
       </c>
@@ -6833,7 +6827,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="410" spans="2:4" hidden="1">
+    <row r="410" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B410" s="1" t="s">
         <v>3</v>
       </c>
@@ -6844,7 +6838,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="411" spans="2:4" hidden="1">
+    <row r="411" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B411" s="1" t="s">
         <v>3</v>
       </c>
@@ -6855,7 +6849,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="412" spans="2:4" hidden="1">
+    <row r="412" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B412" s="1" t="s">
         <v>3</v>
       </c>
@@ -6866,7 +6860,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="413" spans="2:4" hidden="1">
+    <row r="413" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B413" s="1" t="s">
         <v>3</v>
       </c>
@@ -6877,7 +6871,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="414" spans="2:4" hidden="1">
+    <row r="414" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B414" s="1" t="s">
         <v>3</v>
       </c>
@@ -6888,7 +6882,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="415" spans="2:4" hidden="1">
+    <row r="415" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B415" s="1" t="s">
         <v>3</v>
       </c>
@@ -6899,7 +6893,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="416" spans="2:4" hidden="1">
+    <row r="416" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B416" s="1" t="s">
         <v>3</v>
       </c>
@@ -6910,7 +6904,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="417" spans="2:4" hidden="1">
+    <row r="417" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B417" s="1" t="s">
         <v>3</v>
       </c>
@@ -6921,7 +6915,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="418" spans="2:4" hidden="1">
+    <row r="418" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B418" s="1" t="s">
         <v>3</v>
       </c>
@@ -6932,7 +6926,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="419" spans="2:4" hidden="1">
+    <row r="419" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B419" s="1" t="s">
         <v>22</v>
       </c>
@@ -6943,7 +6937,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="420" spans="2:4" hidden="1">
+    <row r="420" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B420" s="1" t="s">
         <v>22</v>
       </c>
@@ -6954,7 +6948,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="421" spans="2:4" hidden="1">
+    <row r="421" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B421" s="1" t="s">
         <v>22</v>
       </c>
@@ -6965,7 +6959,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="422" spans="2:4" hidden="1">
+    <row r="422" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B422" s="1" t="s">
         <v>22</v>
       </c>
@@ -6976,7 +6970,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="423" spans="2:4" hidden="1">
+    <row r="423" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B423" s="1" t="s">
         <v>22</v>
       </c>
@@ -6987,7 +6981,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="424" spans="2:4" hidden="1">
+    <row r="424" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B424" s="1" t="s">
         <v>22</v>
       </c>
@@ -6998,7 +6992,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="425" spans="2:4" hidden="1">
+    <row r="425" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B425" s="1" t="s">
         <v>18</v>
       </c>
@@ -7009,7 +7003,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="426" spans="2:4" hidden="1">
+    <row r="426" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B426" s="1" t="s">
         <v>18</v>
       </c>
@@ -7020,7 +7014,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="427" spans="2:4" hidden="1">
+    <row r="427" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B427" s="1" t="s">
         <v>379</v>
       </c>
@@ -7031,7 +7025,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="428" spans="2:4" hidden="1">
+    <row r="428" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B428" s="1" t="s">
         <v>379</v>
       </c>
@@ -7042,7 +7036,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="429" spans="2:4" hidden="1">
+    <row r="429" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B429" s="1" t="s">
         <v>379</v>
       </c>
@@ -7053,7 +7047,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="430" spans="2:4" hidden="1">
+    <row r="430" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B430" s="1" t="s">
         <v>379</v>
       </c>
@@ -7064,7 +7058,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="431" spans="2:4" hidden="1">
+    <row r="431" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B431" s="1" t="s">
         <v>379</v>
       </c>
@@ -7075,7 +7069,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="432" spans="2:4" hidden="1">
+    <row r="432" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B432" s="1" t="s">
         <v>128</v>
       </c>
@@ -7086,7 +7080,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="433" spans="2:4" hidden="1">
+    <row r="433" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B433" s="1" t="s">
         <v>128</v>
       </c>
@@ -7097,7 +7091,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="434" spans="2:4" hidden="1">
+    <row r="434" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B434" s="1" t="s">
         <v>128</v>
       </c>
@@ -7108,7 +7102,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="435" spans="2:4">
+    <row r="435" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B435" s="1" t="s">
         <v>128</v>
       </c>
@@ -7119,7 +7113,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="436" spans="2:4">
+    <row r="436" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B436" s="1" t="s">
         <v>42</v>
       </c>
@@ -7130,7 +7124,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="437" spans="2:4">
+    <row r="437" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B437" s="1" t="s">
         <v>33</v>
       </c>
@@ -7141,7 +7135,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="438" spans="2:4">
+    <row r="438" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B438" s="1" t="s">
         <v>37</v>
       </c>
@@ -7152,7 +7146,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="439" spans="2:4">
+    <row r="439" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B439" s="1" t="s">
         <v>33</v>
       </c>
@@ -7163,7 +7157,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="440" spans="2:4">
+    <row r="440" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B440" s="1" t="s">
         <v>37</v>
       </c>
@@ -7174,7 +7168,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="441" spans="2:4">
+    <row r="441" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B441" s="1" t="s">
         <v>31</v>
       </c>
@@ -7185,7 +7179,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="442" spans="2:4">
+    <row r="442" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B442" s="1" t="s">
         <v>337</v>
       </c>
@@ -7196,7 +7190,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="443" spans="2:4">
+    <row r="443" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B443" s="1" t="s">
         <v>37</v>
       </c>
@@ -7207,7 +7201,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="444" spans="2:4">
+    <row r="444" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B444" s="1" t="s">
         <v>33</v>
       </c>
@@ -7218,7 +7212,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="445" spans="2:4">
+    <row r="445" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B445" s="1" t="s">
         <v>37</v>
       </c>
@@ -7229,7 +7223,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="446" spans="2:4">
+    <row r="446" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B446" s="1" t="s">
         <v>33</v>
       </c>
@@ -7240,7 +7234,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="447" spans="2:4">
+    <row r="447" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B447" s="1" t="s">
         <v>37</v>
       </c>
@@ -7251,7 +7245,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="448" spans="2:4">
+    <row r="448" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B448" s="1" t="s">
         <v>31</v>
       </c>
@@ -7262,7 +7256,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="449" spans="2:4">
+    <row r="449" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B449" s="1" t="s">
         <v>42</v>
       </c>
@@ -7273,7 +7267,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="450" spans="2:4">
+    <row r="450" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B450" s="1" t="s">
         <v>25</v>
       </c>
@@ -7284,7 +7278,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="451" spans="2:4">
+    <row r="451" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B451" s="1" t="s">
         <v>7</v>
       </c>
@@ -7295,7 +7289,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="452" spans="2:4">
+    <row r="452" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B452" s="1" t="s">
         <v>125</v>
       </c>
@@ -7306,7 +7300,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="453" spans="2:4">
+    <row r="453" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B453" s="1" t="s">
         <v>125</v>
       </c>
@@ -7317,7 +7311,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="454" spans="2:4">
+    <row r="454" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
@@ -7328,7 +7322,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="455" spans="2:4">
+    <row r="455" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B455" s="1" t="s">
         <v>37</v>
       </c>
@@ -7339,7 +7333,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="456" spans="2:4">
+    <row r="456" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B456" s="1" t="s">
         <v>33</v>
       </c>
@@ -7350,7 +7344,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="457" spans="2:4">
+    <row r="457" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B457" s="1" t="s">
         <v>37</v>
       </c>
@@ -7361,7 +7355,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="458" spans="2:4">
+    <row r="458" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B458" s="1" t="s">
         <v>379</v>
       </c>
@@ -7372,7 +7366,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="459" spans="2:4">
+    <row r="459" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B459" s="1" t="s">
         <v>33</v>
       </c>
@@ -7383,7 +7377,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="460" spans="2:4">
+    <row r="460" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B460" s="1" t="s">
         <v>37</v>
       </c>
@@ -7394,7 +7388,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="461" spans="2:4">
+    <row r="461" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B461" s="1" t="s">
         <v>22</v>
       </c>
@@ -7405,7 +7399,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="462" spans="2:4">
+    <row r="462" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B462" s="1" t="s">
         <v>25</v>
       </c>
@@ -7416,7 +7410,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="463" spans="2:4">
+    <row r="463" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B463" s="1" t="s">
         <v>33</v>
       </c>
@@ -7427,7 +7421,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="464" spans="2:4">
+    <row r="464" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B464" s="1" t="s">
         <v>37</v>
       </c>
@@ -7438,7 +7432,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="465" spans="2:4">
+    <row r="465" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B465" s="1" t="s">
         <v>3</v>
       </c>
@@ -7449,7 +7443,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="466" spans="2:4">
+    <row r="466" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B466" s="1" t="s">
         <v>31</v>
       </c>
@@ -7460,7 +7454,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="467" spans="2:4">
+    <row r="467" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B467" s="1" t="s">
         <v>7</v>
       </c>
@@ -7471,7 +7465,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="468" spans="2:4">
+    <row r="468" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B468" s="1" t="s">
         <v>3</v>
       </c>
@@ -7482,7 +7476,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="469" spans="2:4">
+    <row r="469" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B469" s="1" t="s">
         <v>22</v>
       </c>
@@ -7493,7 +7487,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="470" spans="2:4">
+    <row r="470" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B470" s="1" t="s">
         <v>379</v>
       </c>
@@ -7504,7 +7498,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="471" spans="2:4">
+    <row r="471" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B471" s="1" t="s">
         <v>337</v>
       </c>
@@ -7515,7 +7509,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="472" spans="2:4">
+    <row r="472" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B472" s="1" t="s">
         <v>7</v>
       </c>
@@ -7526,7 +7520,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="473" spans="2:4">
+    <row r="473" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B473" s="1" t="s">
         <v>31</v>
       </c>
@@ -7537,7 +7531,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="474" spans="2:4">
+    <row r="474" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B474" s="1" t="s">
         <v>33</v>
       </c>
@@ -7548,7 +7542,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="475" spans="2:4">
+    <row r="475" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B475" s="1" t="s">
         <v>37</v>
       </c>
@@ -7559,7 +7553,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="476" spans="2:4">
+    <row r="476" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B476" s="1" t="s">
         <v>33</v>
       </c>
@@ -7570,7 +7564,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="477" spans="2:4">
+    <row r="477" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B477" s="1" t="s">
         <v>37</v>
       </c>
@@ -7581,7 +7575,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="478" spans="2:4">
+    <row r="478" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B478" s="1" t="s">
         <v>128</v>
       </c>
@@ -7592,7 +7586,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="479" spans="2:4">
+    <row r="479" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B479" s="1" t="s">
         <v>42</v>
       </c>
@@ -7603,7 +7597,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="480" spans="2:4">
+    <row r="480" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B480" s="1" t="s">
         <v>33</v>
       </c>
@@ -7614,7 +7608,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="481" spans="2:4">
+    <row r="481" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B481" s="1" t="s">
         <v>31</v>
       </c>
@@ -7625,7 +7619,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="482" spans="2:4">
+    <row r="482" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B482" s="1" t="s">
         <v>42</v>
       </c>
@@ -7636,7 +7630,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="483" spans="2:4">
+    <row r="483" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B483" s="1" t="s">
         <v>44</v>
       </c>
@@ -7647,7 +7641,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="484" spans="2:4">
+    <row r="484" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B484" s="1" t="s">
         <v>37</v>
       </c>
@@ -7658,7 +7652,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="485" spans="2:4">
+    <row r="485" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B485" s="1" t="s">
         <v>42</v>
       </c>
@@ -7669,7 +7663,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="486" spans="2:4">
+    <row r="486" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B486" s="1" t="s">
         <v>42</v>
       </c>
@@ -7680,7 +7674,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="487" spans="2:4">
+    <row r="487" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B487" s="1" t="s">
         <v>44</v>
       </c>
@@ -7691,7 +7685,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="488" spans="2:4">
+    <row r="488" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B488" s="1" t="s">
         <v>25</v>
       </c>
@@ -7702,7 +7696,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="489" spans="2:4">
+    <row r="489" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B489" s="1" t="s">
         <v>33</v>
       </c>
@@ -7713,7 +7707,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="490" spans="2:4">
+    <row r="490" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B490" s="1" t="s">
         <v>37</v>
       </c>
@@ -7724,7 +7718,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="491" spans="2:4">
+    <row r="491" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B491" s="1" t="s">
         <v>5</v>
       </c>
@@ -7735,7 +7729,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="492" spans="2:4">
+    <row r="492" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B492" s="1" t="s">
         <v>92</v>
       </c>
@@ -7746,7 +7740,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="493" spans="2:4">
+    <row r="493" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B493" s="1" t="s">
         <v>31</v>
       </c>
@@ -7757,7 +7751,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="494" spans="2:4">
+    <row r="494" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B494" s="1" t="s">
         <v>5</v>
       </c>
@@ -7768,7 +7762,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="495" spans="2:4">
+    <row r="495" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B495" s="1" t="s">
         <v>92</v>
       </c>
@@ -7779,7 +7773,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="496" spans="2:4">
+    <row r="496" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B496" s="1" t="s">
         <v>379</v>
       </c>
@@ -7790,7 +7784,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="497" spans="2:4">
+    <row r="497" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B497" s="1" t="s">
         <v>33</v>
       </c>
@@ -7801,7 +7795,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="498" spans="2:4">
+    <row r="498" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B498" s="1" t="s">
         <v>37</v>
       </c>
@@ -7812,7 +7806,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="499" spans="2:4">
+    <row r="499" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B499" s="1" t="s">
         <v>3</v>
       </c>
@@ -7823,7 +7817,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="500" spans="2:4">
+    <row r="500" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B500" s="1" t="s">
         <v>22</v>
       </c>
@@ -7834,7 +7828,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="501" spans="2:4">
+    <row r="501" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B501" s="1" t="s">
         <v>44</v>
       </c>
@@ -7845,7 +7839,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="502" spans="2:4">
+    <row r="502" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B502" s="1" t="s">
         <v>33</v>
       </c>
@@ -7856,7 +7850,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="503" spans="2:4">
+    <row r="503" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B503" s="1" t="s">
         <v>31</v>
       </c>
@@ -7867,7 +7861,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="504" spans="2:4">
+    <row r="504" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B504" s="1" t="s">
         <v>31</v>
       </c>
@@ -7878,7 +7872,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="505" spans="2:4">
+    <row r="505" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B505" s="1" t="s">
         <v>42</v>
       </c>
@@ -7889,7 +7883,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="506" spans="2:4">
+    <row r="506" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B506" s="1" t="s">
         <v>31</v>
       </c>
@@ -7900,7 +7894,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="507" spans="2:4">
+    <row r="507" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B507" s="1" t="s">
         <v>379</v>
       </c>
@@ -7911,7 +7905,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="508" spans="2:4">
+    <row r="508" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B508" s="1" t="s">
         <v>33</v>
       </c>
@@ -7922,7 +7916,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="509" spans="2:4">
+    <row r="509" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B509" s="1" t="s">
         <v>37</v>
       </c>
@@ -7933,7 +7927,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="510" spans="2:4">
+    <row r="510" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B510" s="1" t="s">
         <v>33</v>
       </c>
@@ -7944,7 +7938,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="511" spans="2:4">
+    <row r="511" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B511" s="1" t="s">
         <v>37</v>
       </c>
@@ -7955,7 +7949,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="512" spans="2:4">
+    <row r="512" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B512" s="1" t="s">
         <v>33</v>
       </c>
@@ -7966,7 +7960,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="513" spans="2:4">
+    <row r="513" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B513" s="1" t="s">
         <v>37</v>
       </c>
@@ -7977,7 +7971,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="514" spans="2:4">
+    <row r="514" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B514" s="1" t="s">
         <v>37</v>
       </c>
@@ -7988,7 +7982,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="515" spans="2:4">
+    <row r="515" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B515" s="1" t="s">
         <v>3</v>
       </c>
@@ -7999,7 +7993,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="516" spans="2:4">
+    <row r="516" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B516" s="1" t="s">
         <v>128</v>
       </c>
@@ -8010,7 +8004,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="517" spans="2:4">
+    <row r="517" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B517" s="1" t="s">
         <v>33</v>
       </c>
@@ -8021,7 +8015,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="518" spans="2:4">
+    <row r="518" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B518" s="1" t="s">
         <v>37</v>
       </c>
@@ -8032,7 +8026,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="519" spans="2:4">
+    <row r="519" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B519" s="1" t="s">
         <v>33</v>
       </c>
@@ -8043,7 +8037,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="520" spans="2:4">
+    <row r="520" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B520" s="1" t="s">
         <v>37</v>
       </c>
@@ -8054,7 +8048,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="521" spans="2:4">
+    <row r="521" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B521" s="1" t="s">
         <v>42</v>
       </c>
@@ -8065,7 +8059,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="522" spans="2:4">
+    <row r="522" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B522" s="1" t="s">
         <v>33</v>
       </c>
@@ -8076,7 +8070,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="523" spans="2:4">
+    <row r="523" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B523" s="1" t="s">
         <v>37</v>
       </c>
@@ -8087,7 +8081,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="524" spans="2:4">
+    <row r="524" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B524" s="1" t="s">
         <v>33</v>
       </c>
@@ -8098,7 +8092,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="525" spans="2:4">
+    <row r="525" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B525" s="1" t="s">
         <v>37</v>
       </c>
@@ -8109,7 +8103,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="526" spans="2:4">
+    <row r="526" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B526" s="1" t="s">
         <v>44</v>
       </c>
@@ -8120,7 +8114,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="527" spans="2:4">
+    <row r="527" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B527" s="1" t="s">
         <v>42</v>
       </c>
@@ -8131,7 +8125,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="528" spans="2:4">
+    <row r="528" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B528" s="1" t="s">
         <v>31</v>
       </c>
@@ -8142,7 +8136,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="529" spans="2:4">
+    <row r="529" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B529" s="1" t="s">
         <v>11</v>
       </c>
@@ -8153,7 +8147,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="530" spans="2:4">
+    <row r="530" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B530" s="1" t="s">
         <v>33</v>
       </c>
@@ -8164,7 +8158,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="531" spans="2:4">
+    <row r="531" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B531" s="1" t="s">
         <v>37</v>
       </c>
@@ -8175,7 +8169,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="532" spans="2:4">
+    <row r="532" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B532" s="1" t="s">
         <v>44</v>
       </c>
@@ -8186,7 +8180,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="533" spans="2:4">
+    <row r="533" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B533" s="1" t="s">
         <v>157</v>
       </c>
@@ -8197,7 +8191,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="534" spans="2:4">
+    <row r="534" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B534" s="1" t="s">
         <v>13</v>
       </c>
@@ -8208,7 +8202,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="535" spans="2:4">
+    <row r="535" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B535" s="1" t="s">
         <v>33</v>
       </c>
@@ -8219,7 +8213,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="536" spans="2:4">
+    <row r="536" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B536" s="1" t="s">
         <v>37</v>
       </c>
@@ -8230,7 +8224,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="537" spans="2:4">
+    <row r="537" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B537" s="1" t="s">
         <v>33</v>
       </c>
@@ -8241,7 +8235,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="538" spans="2:4">
+    <row r="538" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B538" s="1" t="s">
         <v>37</v>
       </c>
@@ -8252,15 +8246,15 @@
         <v>464</v>
       </c>
     </row>
-    <row r="539" spans="2:4">
+    <row r="539" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B539" s="1" t="s">
-        <v>465</v>
+        <v>577</v>
       </c>
       <c r="C539" s="3">
         <v>46174</v>
       </c>
       <c r="D539" s="29" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -8275,59 +8269,59 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B82532-6694-4B08-9527-A22A4CBED7A9}">
   <dimension ref="B2:K68"/>
-  <sheetFormatPr defaultColWidth="40.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="40.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="74.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="109.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="109.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="15.6">
+    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="K2" s="12" t="s">
+    </row>
+    <row r="3" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="3" spans="2:11" ht="15.6">
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>477</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>478</v>
       </c>
       <c r="D3" s="15">
         <v>46095</v>
@@ -8336,30 +8330,30 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="J3" s="18" t="s">
         <v>479</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>480</v>
       </c>
       <c r="K3" s="18" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="15.6">
+    <row r="4" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>379</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D4" s="15">
         <v>46113</v>
@@ -8374,24 +8368,24 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="15.6">
+    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D5" s="15">
         <v>46113</v>
@@ -8407,21 +8401,21 @@
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>483</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>484</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="15.6">
+    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D6" s="15">
         <v>46113</v>
@@ -8436,24 +8430,24 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.6">
+    <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D7" s="15">
         <v>46114</v>
@@ -8468,24 +8462,24 @@
         <v>0.3125</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="15.6">
+    <row r="8" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D8" s="15">
         <v>46114</v>
@@ -8500,24 +8494,24 @@
         <v>0.4375</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I8" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>489</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>490</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="15.6">
+    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D9" s="15">
         <v>46114</v>
@@ -8532,24 +8526,24 @@
         <v>0.5229166666666667</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="15.6">
+    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D10" s="15">
         <v>46114</v>
@@ -8564,24 +8558,24 @@
         <v>0.43819444444444444</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I10" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="J10" s="18" t="s">
         <v>489</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>490</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="15.6">
+    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D11" s="15">
         <v>46114</v>
@@ -8596,24 +8590,24 @@
         <v>0.44027777777777777</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="15.6">
+    <row r="12" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D12" s="15">
         <v>46114</v>
@@ -8631,21 +8625,21 @@
         <v>0.44097222222222221</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="15.6">
+    <row r="13" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D13" s="15">
         <v>46114</v>
@@ -8660,24 +8654,24 @@
         <v>0.45416666666666666</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15.6">
+    <row r="14" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D14" s="15">
         <v>46114</v>
@@ -8695,21 +8689,21 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K14" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="15.6">
+    <row r="15" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D15" s="15">
         <v>46114</v>
@@ -8724,24 +8718,24 @@
         <v>0.63402777777777775</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K15" s="18" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="15.6">
+    <row r="16" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D16" s="15">
         <v>46115</v>
@@ -8759,21 +8753,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I16" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>500</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>501</v>
       </c>
       <c r="K16" s="18" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.6">
+    <row r="17" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D17" s="15">
         <v>46116</v>
@@ -8791,21 +8785,21 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="I17" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="K17" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="K17" s="18" t="s">
+    </row>
+    <row r="18" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="13" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="15.6">
-      <c r="B18" s="13" t="s">
-        <v>506</v>
-      </c>
       <c r="C18" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D18" s="15">
         <v>46116</v>
@@ -8820,24 +8814,24 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K18" s="18" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.6">
+    <row r="19" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D19" s="15">
         <v>46117</v>
@@ -8852,24 +8846,24 @@
         <v>0.46875</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K19" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.6">
+    <row r="20" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D20" s="15">
         <v>46117</v>
@@ -8884,24 +8878,24 @@
         <v>0.67847222222222225</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I20" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>510</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>511</v>
       </c>
       <c r="K20" s="18" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.6">
+    <row r="21" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D21" s="15">
         <v>46119</v>
@@ -8919,21 +8913,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.6">
+    <row r="22" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D22" s="15">
         <v>46119</v>
@@ -8948,24 +8942,24 @@
         <v>0.49861111111111112</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K22" s="18" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="15.6">
+    <row r="23" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D23" s="15">
         <v>46119</v>
@@ -8980,24 +8974,24 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I23" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="J23" s="26" t="s">
         <v>515</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>516</v>
       </c>
       <c r="K23" s="18" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="15.6">
+    <row r="24" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D24" s="15">
         <v>46119</v>
@@ -9012,24 +9006,24 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K24" s="18" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="15.6">
+    <row r="25" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D25" s="15">
         <v>46120</v>
@@ -9044,24 +9038,24 @@
         <v>0.32777777777777778</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K25" s="18" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15.6">
+    <row r="26" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D26" s="15">
         <v>46120</v>
@@ -9076,24 +9070,24 @@
         <v>0.65486111111111112</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J26" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K26" s="18" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="15.6">
+    <row r="27" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D27" s="15">
         <v>46121</v>
@@ -9111,21 +9105,21 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I27" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="J27" s="26" t="s">
         <v>522</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>523</v>
       </c>
       <c r="K27" s="18" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.6">
+    <row r="28" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D28" s="15">
         <v>46121</v>
@@ -9140,24 +9134,24 @@
         <v>0.39097222222222222</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I28" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="J28" s="26" t="s">
         <v>524</v>
-      </c>
-      <c r="J28" s="26" t="s">
-        <v>525</v>
       </c>
       <c r="K28" s="18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.6">
+    <row r="29" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D29" s="15">
         <v>46121</v>
@@ -9172,24 +9166,24 @@
         <v>0.43541666666666667</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J29" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="K29" s="18" t="s">
         <v>525</v>
       </c>
-      <c r="K29" s="18" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="15.6">
+    </row>
+    <row r="30" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30" s="14" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D30" s="15">
         <v>46122</v>
@@ -9204,24 +9198,24 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J30" s="26" t="s">
+        <v>526</v>
+      </c>
+      <c r="K30" s="18" t="s">
         <v>527</v>
       </c>
-      <c r="K30" s="18" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" ht="15.6">
+    </row>
+    <row r="31" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D31" s="15">
         <v>46122</v>
@@ -9236,24 +9230,24 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K31" s="18" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.6">
+    <row r="32" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32" s="14" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D32" s="15">
         <v>46123</v>
@@ -9271,21 +9265,21 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="I32" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="J32" s="26" t="s">
         <v>530</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>531</v>
       </c>
       <c r="K32" s="18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.6">
+    <row r="33" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D33" s="15">
         <v>46123</v>
@@ -9300,24 +9294,24 @@
         <v>0.3576388888888889</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K33" s="18" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.6">
+    <row r="34" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34" s="14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D34" s="15">
         <v>46124</v>
@@ -9335,21 +9329,21 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="I34" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="J34" s="26" t="s">
         <v>534</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>535</v>
       </c>
       <c r="K34" s="18" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.6">
+    <row r="35" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D35" s="15">
         <v>46124</v>
@@ -9364,24 +9358,24 @@
         <v>0.29305555555555557</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K35" s="18" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="15.6">
+    <row r="36" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D36" s="15">
         <v>46125</v>
@@ -9399,21 +9393,21 @@
         <v>0.38333333333333336</v>
       </c>
       <c r="I36" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="J36" s="26" t="s">
         <v>539</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>540</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.6">
+    <row r="37" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" s="14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D37" s="15">
         <v>46126</v>
@@ -9428,24 +9422,24 @@
         <v>0.34444444444444444</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K37" s="18" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.6">
+    <row r="38" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D38" s="15">
         <v>46126</v>
@@ -9460,24 +9454,24 @@
         <v>0.34722222222222221</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K38" s="18" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.6">
+    <row r="39" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D39" s="15">
         <v>46129</v>
@@ -9495,21 +9489,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K39" s="24" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="15.6">
+    <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D40" s="15">
         <v>46130</v>
@@ -9518,30 +9512,30 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J40" s="26" t="s">
+        <v>544</v>
+      </c>
+      <c r="K40" s="18" t="s">
         <v>545</v>
       </c>
-      <c r="K40" s="18" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="15.6">
+    </row>
+    <row r="41" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B41" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D41" s="15">
         <v>46130</v>
@@ -9559,21 +9553,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K41" s="18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15.6">
+    <row r="42" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D42" s="15">
         <v>46131</v>
@@ -9591,21 +9585,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I42" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="J42" s="26" t="s">
         <v>548</v>
       </c>
-      <c r="J42" s="26" t="s">
+      <c r="K42" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="K42" s="18" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="15.6">
+    </row>
+    <row r="43" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B43" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D43" s="15">
         <v>46131</v>
@@ -9623,21 +9617,21 @@
         <v>0.375</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K43" s="18" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:11" ht="15.6">
+    <row r="44" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D44" s="15">
         <v>46131</v>
@@ -9655,21 +9649,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I44" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="J44" s="18" t="s">
         <v>551</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>552</v>
       </c>
       <c r="K44" s="18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:11" ht="15.6">
+    <row r="45" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D45" s="15">
         <v>46131</v>
@@ -9687,21 +9681,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K45" s="18" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:11" ht="15.6">
+    <row r="46" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46" s="14" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D46" s="15">
         <v>46132</v>
@@ -9716,24 +9710,24 @@
         <v>0.25624999999999998</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I46" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="J46" s="26" t="s">
         <v>555</v>
-      </c>
-      <c r="J46" s="26" t="s">
-        <v>556</v>
       </c>
       <c r="K46" s="18" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="15.6">
+    <row r="47" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D47" s="15">
         <v>46132</v>
@@ -9748,24 +9742,24 @@
         <v>0.26111111111111113</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K47" s="18" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="48" spans="2:11" ht="15.6">
+    <row r="48" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D48" s="15">
         <v>46134</v>
@@ -9780,24 +9774,24 @@
         <v>0.47083333333333333</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K48" s="18" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="49" spans="2:11" ht="15.6">
+    <row r="49" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D49" s="15">
         <v>46134</v>
@@ -9812,24 +9806,24 @@
         <v>0.49930555555555556</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K49" s="18" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="50" spans="2:11" ht="15.6">
+    <row r="50" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D50" s="15">
         <v>46134</v>
@@ -9844,24 +9838,24 @@
         <v>0.62708333333333333</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K50" s="18" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="51" spans="2:11" ht="15.6">
+    <row r="51" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B51" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D51" s="15">
         <v>46135</v>
@@ -9879,21 +9873,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K51" s="18" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="2:11" ht="15.6">
+    <row r="52" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B52" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D52" s="15">
         <v>46135</v>
@@ -9911,21 +9905,21 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K52" s="18" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="53" spans="2:11" ht="15.6">
+    <row r="53" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B53" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D53" s="15">
         <v>46136</v>
@@ -9934,30 +9928,30 @@
         <v>0.25</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J53" s="26" t="s">
+        <v>559</v>
+      </c>
+      <c r="K53" s="18" t="s">
         <v>560</v>
       </c>
-      <c r="K53" s="18" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" ht="15.6">
+    </row>
+    <row r="54" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B54" s="14" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D54" s="15">
         <v>46136</v>
@@ -9966,30 +9960,30 @@
         <v>0.25</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G54" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J54" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="K54" s="18" t="s">
         <v>562</v>
       </c>
-      <c r="K54" s="18" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" ht="15.6">
+    </row>
+    <row r="55" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B55" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D55" s="15">
         <v>46136</v>
@@ -10006,18 +10000,18 @@
       <c r="H55" s="16"/>
       <c r="I55" s="14"/>
       <c r="J55" s="26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K55" s="18" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:11" ht="15.6">
+    <row r="56" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B56" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D56" s="15">
         <v>46136</v>
@@ -10032,24 +10026,24 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K56" s="18" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="2:11" ht="15.6">
+    <row r="57" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B57" s="14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D57" s="15">
         <v>46137</v>
@@ -10058,30 +10052,30 @@
         <v>0.25</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J57" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="K57" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="K57" s="18" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" ht="15.6">
+    </row>
+    <row r="58" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B58" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D58" s="15">
         <v>46137</v>
@@ -10096,24 +10090,24 @@
         <v>0.51458333333333328</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K58" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="59" spans="2:11" ht="15.6">
+    <row r="59" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B59" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D59" s="15">
         <v>46137</v>
@@ -10131,21 +10125,21 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K59" s="18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="2:11" ht="15.6">
+    <row r="60" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B60" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D60" s="15">
         <v>46138</v>
@@ -10160,24 +10154,24 @@
         <v>0.3125</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K60" s="18" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="2:11" ht="15.6">
+    <row r="61" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B61" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D61" s="15">
         <v>46139</v>
@@ -10192,24 +10186,24 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J61" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="K61" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="K61" s="18" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" ht="15.6">
+    </row>
+    <row r="62" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D62" s="15">
         <v>46139</v>
@@ -10227,21 +10221,21 @@
         <v>0.65625</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J62" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K62" s="18" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="63" spans="2:11" ht="15.6">
+    <row r="63" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B63" s="13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D63" s="15">
         <v>46139</v>
@@ -10256,24 +10250,24 @@
         <v>0.30555555555555558</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K63" s="18" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="2:11" ht="15.6">
+    <row r="64" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B64" s="14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D64" s="15">
         <v>46140</v>
@@ -10288,24 +10282,24 @@
         <v>0.75555555555555554</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K64" s="18" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="65" spans="2:11" ht="15.6">
+    <row r="65" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B65" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D65" s="15">
         <v>46141</v>
@@ -10323,21 +10317,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K65" s="18" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="66" spans="2:11" ht="15.6">
+    <row r="66" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B66" s="14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D66" s="15">
         <v>46141</v>
@@ -10355,21 +10349,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K66" s="18" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="2:11" ht="15.6">
+    <row r="67" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B67" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D67" s="15">
         <v>46141</v>
@@ -10384,24 +10378,24 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K67" s="18" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="2:11" ht="15.6">
+    <row r="68" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B68" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D68" s="15">
         <v>46141</v>
@@ -10417,10 +10411,10 @@
       </c>
       <c r="H68" s="16"/>
       <c r="I68" s="14" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K68" s="18" t="s">
         <v>258</v>
@@ -10448,15 +10442,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100129872B20EB72F43A65F017F96B1C226" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8918ff54d439e714c6ec094a8552ca51">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae836115-58a4-4701-a509-51b7f29d6ef2" xmlns:ns3="f2c58eb1-9d7f-4123-980d-e0326d949ea4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dac983c0446f866ea106b147c21f2a9" ns2:_="" ns3:_="">
     <xsd:import namespace="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
@@ -10716,14 +10701,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D474CDF3-F77E-4C91-BAE3-2259CB3B5596}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D474CDF3-F77E-4C91-BAE3-2259CB3B5596}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
+    <ds:schemaRef ds:uri="f2c58eb1-9d7f-4123-980d-e0326d949ea4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{479B8213-A263-4381-AC21-345AF9A36A7B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
+    <ds:schemaRef ds:uri="f2c58eb1-9d7f-4123-980d-e0326d949ea4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{479B8213-A263-4381-AC21-345AF9A36A7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>